--- a/堆龙待编码测点.xlsx
+++ b/堆龙待编码测点.xlsx
@@ -32,7 +32,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5383" uniqueCount="923">
   <si>
-    <t>名称</t>
+    <t>测点描述</t>
   </si>
   <si>
     <t>场站名称</t>
@@ -3968,6 +3968,7 @@
     <col min="1" max="1" width="55.2788461538462" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5961538461538" customWidth="1"/>
     <col min="3" max="3" width="14.7403846153846" customWidth="1"/>
+    <col min="4" max="4" width="13.7788461538462" customWidth="1"/>
     <col min="5" max="5" width="12.3269230769231" customWidth="1"/>
     <col min="6" max="6" width="12.0096153846154" customWidth="1"/>
     <col min="7" max="7" width="13.6153846153846" customWidth="1"/>
